--- a/templates/douches.xlsx
+++ b/templates/douches.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Joris\gb-etats-des-lieux\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Joris\gb-etats-des-lieux\modeles_reels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4068C75D-336A-405E-9659-70896F2F5AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFF7C77A-D44D-4F36-820A-3175BA7C2B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="12660" xr2:uid="{32D17F47-F6AA-46C2-AFF4-B33E431CFF6B}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="12660" activeTab="1" xr2:uid="{32D17F47-F6AA-46C2-AFF4-B33E431CFF6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Grand Sanitaire Douche" sheetId="2" r:id="rId1"/>
+    <sheet name="Petit Sanitaire Douche" sheetId="8" r:id="rId2"/>
+    <sheet name="INFOS" sheetId="10" r:id="rId3"/>
+    <sheet name="Grand Sanit 4 Douches A01189" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="72">
   <si>
     <t>ETAT INTERIEUR</t>
   </si>
@@ -153,10 +156,16 @@
     <t xml:space="preserve">CHANTIER : </t>
   </si>
   <si>
+    <t>W ….…………..…..</t>
+  </si>
+  <si>
     <t>N° CE :</t>
   </si>
   <si>
     <t>Nom préparateur :                                         Visa contrôleur :                                          Date :</t>
+  </si>
+  <si>
+    <t>Sanitaire : BLOC .. DOUCHES</t>
   </si>
   <si>
     <t>Sanitaire : BLOC 6 DOUCHES</t>
@@ -212,14 +221,142 @@
     <t>Contrôle fixations du chauffe-eau (en atelier)</t>
   </si>
   <si>
+    <t>Sanitaire : BLOC 4 DOUCHES</t>
+  </si>
+  <si>
+    <t>A 01189</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLIENT : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">diam sortie : </t>
+  </si>
+  <si>
+    <t>IMPORTANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE BUNGALOW VOUS EST LIVRÉ PROPRE ET EN ÉTAT DE MARCHE. </t>
+  </si>
+  <si>
+    <t>IL A ÉTÉ VÉRIFIÉ AVANT LIVRAISON</t>
+  </si>
+  <si>
+    <r>
+      <t>RACCORDEMENT</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t> :</t>
+    </r>
+  </si>
+  <si>
+    <t>- Les groupes de sécurité sont réglés à 3 bars. Ne pas dépasser cette pression !</t>
+  </si>
+  <si>
+    <t>- La mise en eau doit être effectué avant le branchement en électricité !</t>
+  </si>
+  <si>
+    <r>
+      <t>L’HIVER</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t> :</t>
+    </r>
+  </si>
+  <si>
+    <t>- IL EST IMPERATIF QUE LE BUNGALOW SOIT CHAUFFÉ AFIN QUE LES TUYAUX    NE GELENT PAS ! Ouvrir le robinet de purge sous le lavabo.</t>
+  </si>
+  <si>
+    <r>
+      <t>RETOUR DU BUNGALOW</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t> :</t>
+    </r>
+  </si>
+  <si>
+    <t>- Le sanitaire doit être débranché en eau et en électricité.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>La vidange du cumulus est obligatoire avant toute manutention !</t>
+    </r>
+  </si>
+  <si>
+    <t>- Il vous est demandé de nettoyer ce bungalow.</t>
+  </si>
+  <si>
+    <t>Si problème merci de nous contacter au 05.58.57.39.00</t>
+  </si>
+  <si>
+    <t>TOUTES DÉGRADATIONS VOUS SERONT FACTURÉES !</t>
+  </si>
+  <si>
+    <t>- La vidange du cumulus est obligatoire avant toute manutention !</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>La mise en eau doit être effectué avant le branchement en électricité</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> - IL EST IMPERATIF QUE LE BUNGALOW SOIT CHAUFFÉ AFIN QUE LES TUYAUX NE GELENT PAS ! Ouvrir le robinet de purge sous le lavabo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -278,6 +415,122 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -600,191 +853,286 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1089,6 +1437,847 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D9EBEFE-367F-FAE4-657F-2343A9C3B6C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11393" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05368075-AE49-D1F6-D6A4-870B63822E67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4086225" y="1819275"/>
+          <a:ext cx="1524000" cy="1066800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11394" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73661FC3-6AF3-2B70-C06D-BB87653A22AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="723900" y="1838325"/>
+          <a:ext cx="1485900" cy="1038225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB5A72A1-6B8B-EC7C-458F-6D054BA01506}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3248025" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE3CE094-0AE1-F197-7A44-997CF648B344}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11397" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6870D4E-A140-BCBE-460E-91B937710C00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="0"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11398" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF3283EB-5C1D-C73F-FCE8-48C6C41C9266}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="10620375"/>
+          <a:ext cx="3124200" cy="866775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13319" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{259AE18B-C407-05AE-B5BE-C72992C006B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="476250"/>
+          <a:ext cx="3028950" cy="1066800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12354" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{167C300F-D001-A309-18CA-F8700E783A24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3238500" y="2257425"/>
+          <a:ext cx="2676525" cy="1238250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12355" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FB7003C-1D9E-7977-F074-78506C945CF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2286000"/>
+          <a:ext cx="2667000" cy="1257300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1939232C-EC22-6EBA-B3F3-4D6888F8DF7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3248025" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41C86029-B680-3CE4-5019-232A7A59801B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12358" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04D92F83-354C-5A72-C976-E2E38D9B428B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1498,7 +2687,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
@@ -1506,645 +2695,716 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="65" t="s">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="103" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="14"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="105"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="10"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="68"/>
-    </row>
-    <row r="9" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="69" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
     </row>
     <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="54"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="86"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
     </row>
     <row r="12" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="78"/>
-      <c r="B19" s="78"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="8"/>
+      <c r="F22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6" t="s">
+      <c r="G22" s="8"/>
+      <c r="H22" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="63" t="s">
+      <c r="B24" s="93"/>
+      <c r="C24" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="63" t="s">
+      <c r="D24" s="46"/>
+      <c r="E24" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="F24" s="64"/>
-      <c r="G24" s="63" t="s">
+      <c r="F24" s="46"/>
+      <c r="G24" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="64"/>
+      <c r="H24" s="46"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="55" t="s">
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
     </row>
     <row r="26" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="46"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" spans="1:8" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="60"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="49"/>
+      <c r="A27" s="90"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="80"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="46"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="46"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="47"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="49"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="80"/>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23" t="s">
+      <c r="A30" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="51"/>
+      <c r="C30" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="23" t="s">
+      <c r="D30" s="48"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="24"/>
-      <c r="H30" s="25"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
     </row>
     <row r="31" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23" t="s">
+      <c r="B31" s="51"/>
+      <c r="C31" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="23" t="s">
+      <c r="D31" s="48"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G31" s="24"/>
-      <c r="H31" s="25"/>
-    </row>
-    <row r="32" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="1"/>
-      <c r="H32" s="4"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
+    </row>
+    <row r="32" spans="1:8" s="1" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="52" t="s">
+      <c r="A33" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="54"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="86"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="55" t="s">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="55" t="s">
+      <c r="D34" s="43"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="56"/>
-      <c r="H34" s="57"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
     </row>
     <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="36" t="s">
+      <c r="A35" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="41"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="46"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="42"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="49"/>
+      <c r="A36" s="72"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="80"/>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="25"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="49"/>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="37"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="40"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="83"/>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="29"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="60"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="29"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="60"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="29"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="60"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="29"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="60"/>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="29"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="60"/>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="29"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="60"/>
     </row>
     <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="29"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60"/>
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="29"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="60"/>
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="29"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="60"/>
     </row>
     <row r="48" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="26"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="60"/>
     </row>
     <row r="49" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="70" t="s">
+      <c r="A49" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="54"/>
+      <c r="C49" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="56"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="69"/>
+    </row>
+    <row r="50" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="54"/>
+      <c r="C50" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="72" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="73"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="75"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="77"/>
-    </row>
-    <row r="50" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="71"/>
-      <c r="C50" s="72" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="73"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="75"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="77"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="69"/>
     </row>
     <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="26"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="29"/>
-    </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="19" t="s">
+      <c r="B51" s="37"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="60"/>
+    </row>
+    <row r="52" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="29"/>
-    </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="19" t="s">
+      <c r="B52" s="37"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="60"/>
+    </row>
+    <row r="53" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B53" s="20"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="35"/>
-    </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="19" t="s">
+      <c r="B53" s="66"/>
+      <c r="C53" s="100"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="102"/>
+      <c r="F53" s="100"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="102"/>
+    </row>
+    <row r="54" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="35"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="100"/>
+      <c r="D54" s="101"/>
+      <c r="E54" s="102"/>
+      <c r="F54" s="100"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="102"/>
     </row>
     <row r="55" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="19" t="s">
+      <c r="A55" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="32"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="97"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="97"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="99"/>
     </row>
     <row r="56" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B56" s="16"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="18"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="64"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="65"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="68" t="s">
+      <c r="A58" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="68" t="s">
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="F58" s="68"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="68"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B61" s="78"/>
-      <c r="C61" s="78"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="78" t="s">
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="F61" s="78"/>
-      <c r="G61" s="78"/>
-      <c r="H61" s="78"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="E2:H4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F26:H27"/>
+    <mergeCell ref="C28:E29"/>
+    <mergeCell ref="F28:H29"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F35:H36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A26:B27"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="C26:E27"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C35:E36"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C46:E46"/>
     <mergeCell ref="A61:D61"/>
     <mergeCell ref="E61:H61"/>
     <mergeCell ref="A56:H56"/>
@@ -2156,81 +3416,25 @@
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="E58:H58"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="C50:E50"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
     <mergeCell ref="C51:E51"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C35:E36"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:H42"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F26:H27"/>
-    <mergeCell ref="C28:E29"/>
-    <mergeCell ref="F28:H29"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F35:H36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A26:B27"/>
-    <mergeCell ref="A28:B29"/>
-    <mergeCell ref="C26:E27"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C34:E34"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.19" right="0.21" top="0.18" bottom="0.19" header="0.16" footer="0.15"/>
@@ -2238,4 +3442,1806 @@
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFD17D7-2EC6-4D89-A55D-03609392C313}">
+  <dimension ref="A1:H81"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="8" width="13.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+    </row>
+    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+    </row>
+    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="105"/>
+    </row>
+    <row r="8" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="85"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="86"/>
+    </row>
+    <row r="10" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="107" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="107"/>
+      <c r="C10" s="107"/>
+    </row>
+    <row r="11" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="93"/>
+      <c r="C20" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="46"/>
+      <c r="E20" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="46"/>
+      <c r="G20" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="46"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
+    </row>
+    <row r="22" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="89"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="77"/>
+    </row>
+    <row r="23" spans="1:8" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="90"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="80"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="94"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="77"/>
+    </row>
+    <row r="25" spans="1:8" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="95"/>
+      <c r="B25" s="96"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="80"/>
+    </row>
+    <row r="26" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="51"/>
+      <c r="C26" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="48"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="48"/>
+      <c r="H26" s="49"/>
+    </row>
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="51"/>
+      <c r="C27" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="48"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
+    </row>
+    <row r="28" spans="1:8" s="1" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="86"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="43"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
+    </row>
+    <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="71"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="77"/>
+    </row>
+    <row r="32" spans="1:8" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="72"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="80"/>
+    </row>
+    <row r="33" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="41"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="49"/>
+    </row>
+    <row r="34" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="74"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="83"/>
+    </row>
+    <row r="35" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="37"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="60"/>
+    </row>
+    <row r="36" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="37"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="60"/>
+    </row>
+    <row r="37" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="37"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="60"/>
+    </row>
+    <row r="38" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="37"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="60"/>
+    </row>
+    <row r="39" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="60"/>
+    </row>
+    <row r="40" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="60"/>
+    </row>
+    <row r="41" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="60"/>
+    </row>
+    <row r="42" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="37"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="60"/>
+    </row>
+    <row r="43" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="37"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="60"/>
+    </row>
+    <row r="44" spans="1:8" ht="17.850000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="37"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="60"/>
+    </row>
+    <row r="45" spans="1:8" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="54"/>
+      <c r="C45" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="56"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="69"/>
+    </row>
+    <row r="46" spans="1:8" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="54"/>
+      <c r="C46" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="56"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="69"/>
+    </row>
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="37"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="60"/>
+    </row>
+    <row r="48" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="37"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="60"/>
+    </row>
+    <row r="49" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="66"/>
+      <c r="C49" s="100"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="102"/>
+      <c r="F49" s="100"/>
+      <c r="G49" s="101"/>
+      <c r="H49" s="102"/>
+    </row>
+    <row r="50" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="66"/>
+      <c r="C50" s="100"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="102"/>
+      <c r="F50" s="100"/>
+      <c r="G50" s="101"/>
+      <c r="H50" s="102"/>
+    </row>
+    <row r="51" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="37"/>
+      <c r="C51" s="97" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="98"/>
+      <c r="E51" s="99"/>
+      <c r="F51" s="97"/>
+      <c r="G51" s="98"/>
+      <c r="H51" s="99"/>
+    </row>
+    <row r="52" spans="1:8" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" s="63"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="65"/>
+    </row>
+    <row r="53" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="114" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="114"/>
+      <c r="C53" s="114"/>
+      <c r="D53" s="114"/>
+      <c r="E53" s="114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="114"/>
+      <c r="G53" s="114"/>
+      <c r="H53" s="114"/>
+    </row>
+    <row r="54" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="108" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="108"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="108"/>
+      <c r="E54" s="108" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="108"/>
+      <c r="G54" s="108"/>
+      <c r="H54" s="108"/>
+    </row>
+    <row r="55" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="61" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="20"/>
+    </row>
+    <row r="62" spans="1:8" ht="61.5" x14ac:dyDescent="0.2">
+      <c r="A62" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="109"/>
+      <c r="C62" s="109"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="109"/>
+      <c r="H62" s="109"/>
+    </row>
+    <row r="63" spans="1:8" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="23"/>
+    </row>
+    <row r="64" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+      <c r="A64" s="110" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="110"/>
+      <c r="C64" s="110"/>
+      <c r="D64" s="110"/>
+      <c r="E64" s="110"/>
+      <c r="F64" s="110"/>
+      <c r="G64" s="110"/>
+      <c r="H64" s="110"/>
+    </row>
+    <row r="65" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="25"/>
+    </row>
+    <row r="66" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+      <c r="A66" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A67" s="111" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" s="111"/>
+      <c r="C67" s="111"/>
+      <c r="D67" s="111"/>
+      <c r="E67" s="111"/>
+      <c r="F67" s="111"/>
+      <c r="G67" s="111"/>
+      <c r="H67" s="111"/>
+    </row>
+    <row r="68" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A68" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="112"/>
+      <c r="C68" s="112"/>
+      <c r="D68" s="112"/>
+      <c r="E68" s="112"/>
+      <c r="F68" s="112"/>
+      <c r="G68" s="112"/>
+      <c r="H68" s="112"/>
+    </row>
+    <row r="69" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="25"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="34"/>
+      <c r="H69" s="34"/>
+    </row>
+    <row r="70" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+      <c r="A70" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="113" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="113"/>
+      <c r="C71" s="113"/>
+      <c r="D71" s="113"/>
+      <c r="E71" s="113"/>
+      <c r="F71" s="113"/>
+      <c r="G71" s="113"/>
+      <c r="H71" s="113"/>
+    </row>
+    <row r="72" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="113"/>
+      <c r="B72" s="113"/>
+      <c r="C72" s="113"/>
+      <c r="D72" s="113"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="113"/>
+      <c r="G72" s="113"/>
+      <c r="H72" s="113"/>
+    </row>
+    <row r="73" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="35"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="35"/>
+    </row>
+    <row r="74" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+      <c r="A74" s="26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A75" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A76" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B76" s="31"/>
+      <c r="C76" s="31"/>
+      <c r="D76" s="31"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+    </row>
+    <row r="77" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A77" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A78" s="25"/>
+    </row>
+    <row r="79" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A79" s="25"/>
+    </row>
+    <row r="80" spans="1:8" ht="26.25" x14ac:dyDescent="0.2">
+      <c r="A80" s="32"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="33"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="98">
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A71:H72"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:E32"/>
+    <mergeCell ref="F31:H32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:E23"/>
+    <mergeCell ref="F22:H23"/>
+    <mergeCell ref="A24:B25"/>
+    <mergeCell ref="C24:E25"/>
+    <mergeCell ref="F24:H25"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="E1:H3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="F46:H46"/>
+  </mergeCells>
+  <pageMargins left="0.19" right="0.21" top="0.18" bottom="0.19" header="0.16" footer="0.15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BFE65D9-6934-4910-B213-0EF1DEA61F3F}">
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="19"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="21"/>
+    </row>
+    <row r="11" spans="1:8" ht="61.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+    </row>
+    <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+      <c r="A13" s="24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="25"/>
+    </row>
+    <row r="16" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+      <c r="A16" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21" x14ac:dyDescent="0.2">
+      <c r="A19" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="115" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="115"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+    </row>
+    <row r="22" spans="1:7" ht="21" x14ac:dyDescent="0.2">
+      <c r="A22" s="26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="25"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="25"/>
+    </row>
+    <row r="29" spans="1:7" ht="26.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:G20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966E9678-8756-49CE-932F-2E50BD2FE4B2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="8" width="13.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="103" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="14"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+    </row>
+    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="105"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="106"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="86"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="107" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
+    </row>
+    <row r="12" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="93"/>
+      <c r="C24" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="46"/>
+      <c r="E24" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="46"/>
+      <c r="G24" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="46"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
+    </row>
+    <row r="26" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="89"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="77"/>
+    </row>
+    <row r="27" spans="1:8" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="90"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="80"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="94"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="77"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="95"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="80"/>
+    </row>
+    <row r="30" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="51"/>
+      <c r="C30" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="48"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
+    </row>
+    <row r="31" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="51"/>
+      <c r="C31" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="48"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
+    </row>
+    <row r="32" spans="1:8" s="1" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="86"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="43"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+    </row>
+    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="71"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="77"/>
+    </row>
+    <row r="36" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="72"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="80"/>
+    </row>
+    <row r="37" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="41"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="49"/>
+    </row>
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="74"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="83"/>
+    </row>
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="37"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="60"/>
+    </row>
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="37"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="60"/>
+    </row>
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="60"/>
+    </row>
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="37"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="60"/>
+    </row>
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="60"/>
+    </row>
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="60"/>
+    </row>
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="37"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60"/>
+    </row>
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="37"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="60"/>
+    </row>
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="37"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="60"/>
+    </row>
+    <row r="48" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="37"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="60"/>
+    </row>
+    <row r="49" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="54"/>
+      <c r="C49" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="56"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="69"/>
+    </row>
+    <row r="50" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="54"/>
+      <c r="C50" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="56"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="69"/>
+    </row>
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="37"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="60"/>
+    </row>
+    <row r="52" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="37"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="60"/>
+    </row>
+    <row r="53" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" s="66"/>
+      <c r="C53" s="100"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="102"/>
+      <c r="F53" s="100"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="102"/>
+    </row>
+    <row r="54" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="66"/>
+      <c r="C54" s="100"/>
+      <c r="D54" s="101"/>
+      <c r="E54" s="102"/>
+      <c r="F54" s="100"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="102"/>
+    </row>
+    <row r="55" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="37"/>
+      <c r="C55" s="97"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="97"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="99"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="63"/>
+      <c r="C56" s="64"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="65"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" s="52"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="95">
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A26:B27"/>
+    <mergeCell ref="C26:E27"/>
+    <mergeCell ref="F26:H27"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="C28:E29"/>
+    <mergeCell ref="F28:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:E36"/>
+    <mergeCell ref="F35:H36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:E55"/>
+  </mergeCells>
+  <pageMargins left="0.19" right="0.21" top="0.18" bottom="0.19" header="0.16" footer="0.15"/>
+  <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>